--- a/chapters/ch03/data/QUA107_CH03_Data.xlsx
+++ b/chapters/ch03/data/QUA107_CH03_Data.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="106">
   <si>
     <t xml:space="preserve">QUA 107 · Chapter 3 · Describing Data: Numerical Measures · data workbook</t>
   </si>
@@ -330,16 +330,22 @@
     <t xml:space="preserve">Branch 15</t>
   </si>
   <si>
-    <t xml:space="preserve">Q1  (position (15+1)·25/100 = 4 of the sorted list)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Median (position 8)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q3  (position 12)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Note: with n = 15, (n + 1) = 16, so the quartile locations 4, 8 and 12 are whole numbers.</t>
+    <t xml:space="preserve">Q1 = QUARTILE.EXC(range, 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Median = QUARTILE.EXC(range, 2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q3 = QUARTILE.EXC(range, 3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P90 = PERCENTILE.EXC(range, 0.9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Note: the .EXC functions use the same (n + 1) method as the slides: with n = 15 the quartile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">locations (16 × 25/100 = 4, 8, 12) are whole numbers, so Q1, the median and Q3 are the 4th, 8th and 12th sorted values.</t>
   </si>
 </sst>
 </file>
@@ -2285,7 +2291,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
@@ -2500,7 +2506,7 @@
         <v>100</v>
       </c>
       <c r="B19" s="3" t="n">
-        <f aca="false">SMALL(B2:B16,4)</f>
+        <f aca="false">_xlfn.QUARTILE.EXC(B2:B16,1)</f>
         <v>172</v>
       </c>
     </row>
@@ -2509,7 +2515,7 @@
         <v>101</v>
       </c>
       <c r="B20" s="3" t="n">
-        <f aca="false">MEDIAN(B2:B16)</f>
+        <f aca="false">_xlfn.QUARTILE.EXC(B2:B16,2)</f>
         <v>204</v>
       </c>
     </row>
@@ -2518,7 +2524,7 @@
         <v>102</v>
       </c>
       <c r="B21" s="3" t="n">
-        <f aca="false">SMALL(B2:B16,12)</f>
+        <f aca="false">_xlfn.QUARTILE.EXC(B2:B16,3)</f>
         <v>220</v>
       </c>
     </row>
@@ -2531,9 +2537,23 @@
         <v>240</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="4" t="s">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="6" t="s">
         <v>103</v>
+      </c>
+      <c r="B23" s="3" t="n">
+        <f aca="false">_xlfn.PERCENTILE.EXC(B2:B16,0.9)</f>
+        <v>234.6</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="4" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>

--- a/chapters/ch03/data/QUA107_CH03_Data.xlsx
+++ b/chapters/ch03/data/QUA107_CH03_Data.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="104">
   <si>
     <t xml:space="preserve">QUA 107 · Chapter 3 · Describing Data: Numerical Measures · data workbook</t>
   </si>
@@ -330,22 +330,16 @@
     <t xml:space="preserve">Branch 15</t>
   </si>
   <si>
-    <t xml:space="preserve">Q1 = QUARTILE.EXC(range, 1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Median = QUARTILE.EXC(range, 2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q3 = QUARTILE.EXC(range, 3)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P90 = PERCENTILE.EXC(range, 0.9)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Note: the .EXC functions use the same (n + 1) method as the slides: with n = 15 the quartile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">locations (16 × 25/100 = 4, 8, 12) are whole numbers, so Q1, the median and Q3 are the 4th, 8th and 12th sorted values.</t>
+    <t xml:space="preserve">Q1  (position (15+1)·25/100 = 4 of the sorted list)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Median (position 8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q3  (position 12)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Note: with n = 15, (n + 1) = 16, so the quartile locations 4, 8 and 12 are whole numbers.</t>
   </si>
 </sst>
 </file>
@@ -2291,7 +2285,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
@@ -2506,7 +2500,7 @@
         <v>100</v>
       </c>
       <c r="B19" s="3" t="n">
-        <f aca="false">_xlfn.QUARTILE.EXC(B2:B16,1)</f>
+        <f aca="false">SMALL(B2:B16,4)</f>
         <v>172</v>
       </c>
     </row>
@@ -2515,7 +2509,7 @@
         <v>101</v>
       </c>
       <c r="B20" s="3" t="n">
-        <f aca="false">_xlfn.QUARTILE.EXC(B2:B16,2)</f>
+        <f aca="false">MEDIAN(B2:B16)</f>
         <v>204</v>
       </c>
     </row>
@@ -2524,7 +2518,7 @@
         <v>102</v>
       </c>
       <c r="B21" s="3" t="n">
-        <f aca="false">_xlfn.QUARTILE.EXC(B2:B16,3)</f>
+        <f aca="false">SMALL(B2:B16,12)</f>
         <v>220</v>
       </c>
     </row>
@@ -2537,23 +2531,9 @@
         <v>240</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="6" t="s">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="4" t="s">
         <v>103</v>
-      </c>
-      <c r="B23" s="3" t="n">
-        <f aca="false">_xlfn.PERCENTILE.EXC(B2:B16,0.9)</f>
-        <v>234.6</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="4" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="4" t="s">
-        <v>105</v>
       </c>
     </row>
   </sheetData>
